--- a/artfynd/A 20124-2023 artfynd.xlsx
+++ b/artfynd/A 20124-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20124-2023 artfynd.xlsx
+++ b/artfynd/A 20124-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>90848734</v>
+        <v>90848715</v>
       </c>
       <c r="B2" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99456</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>222741</v>
+        <v>219880</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Kransrams</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Polygonatum verticillatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
+          <t>(L.) All.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>459876.1100251653</v>
+        <v>459802</v>
       </c>
       <c r="R2" t="n">
-        <v>7001236.124638243</v>
+        <v>7001273</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>2019-08-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-08-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110231597</v>
+        <v>110231410</v>
       </c>
       <c r="B3" t="n">
-        <v>95661</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>103683</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,25 +787,33 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>222741</v>
+        <v>222002</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Finbräken</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cystopteris montana</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Lam.) Desv.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
@@ -835,10 +823,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>459870.2286925202</v>
+        <v>459797</v>
       </c>
       <c r="R3" t="n">
-        <v>7001236.649821412</v>
+        <v>7001225</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,19 +856,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -895,7 +873,7 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Kallkälldråg med rörligt grundvatten.</t>
+          <t>Nära bäck</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -913,15 +891,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110231410</v>
+        <v>90848734</v>
       </c>
       <c r="B4" t="n">
-        <v>101120</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,46 +902,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>222002</v>
+        <v>222741</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>(Lam.) Desv.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bäck, Jmt</t>
+          <t>Låsböle, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>459797.6112416872</v>
+        <v>459876</v>
       </c>
       <c r="R4" t="n">
-        <v>7001224.43433952</v>
+        <v>7001236</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -995,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1019,39 +970,32 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>Nära bäck</t>
-        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Christer Pålsson</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr"/>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110231252</v>
+        <v>110231597</v>
       </c>
       <c r="B5" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98137</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,30 +1003,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222771</v>
+        <v>222741</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Finbräken</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Cystopteris montana</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Lam.) Desv.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
@@ -1091,10 +1031,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>459801.733714317</v>
+        <v>459870</v>
       </c>
       <c r="R5" t="n">
-        <v>7001264.636760492</v>
+        <v>7001236</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1124,19 +1064,9 @@
           <t>2023-06-20</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,6 +1078,11 @@
       <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kallkälldråg med rörligt grundvatten.</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1164,15 +1099,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110231370</v>
+        <v>90848714</v>
       </c>
       <c r="B6" t="n">
-        <v>98431</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1198,24 +1128,16 @@
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Bäck, Jmt</t>
+          <t>Låsböle, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>459797.6112416872</v>
+        <v>459802</v>
       </c>
       <c r="R6" t="n">
-        <v>7001224.43433952</v>
+        <v>7001273</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1242,22 +1164,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2019-08-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1266,22 +1178,344 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Via Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>110231252</v>
+      </c>
+      <c r="B7" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bäck, Jmt</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>459802</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7001264</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
           <t>Christer Pålsson</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>Christer Pålsson</t>
         </is>
       </c>
-      <c r="AY6" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>110231370</v>
+      </c>
+      <c r="B8" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bäck, Jmt</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>459797</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7001225</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Christer Pålsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Christer Pålsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>110233830</v>
+      </c>
+      <c r="B9" t="n">
+        <v>97921</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>233219</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vågig rutlungmossa</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Conocephalum salebrosum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Szweyk., Buczk. &amp; Odrzyk.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bäck, Jmt</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>459870</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7001236</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Åre</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Marby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>I en lodrätt kant i skuggigt läge intill en kallkälla.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Christer Pålsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Christer Pålsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20124-2023 artfynd.xlsx
+++ b/artfynd/A 20124-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848715</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -888,6 +898,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231410</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -987,6 +1002,11 @@
       <c r="AY4" t="inlineStr">
         <is>
           <t>Kalkbarrskogar i Jämtlands län</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848734</t>
         </is>
       </c>
     </row>
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231597</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1197,6 +1222,11 @@
           <t>Kalkbarrskogar i Jämtlands län</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/90848714</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1303,6 +1333,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231252</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1409,6 +1444,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110231370</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1516,8 +1556,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110233830</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>